--- a/00_sample/模板测算表/节能评估表-按冷站电量数据-二次泵版.xlsx
+++ b/00_sample/模板测算表/节能评估表-按冷站电量数据-二次泵版.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="27660" windowHeight="15180"/>
   </bookViews>
   <sheets>
-    <sheet name="【1】按冷站电量数据-上限 " sheetId="1" r:id="rId1"/>
+    <sheet name="【1】按冷站电量数据-上限" sheetId="1" r:id="rId1"/>
     <sheet name="【2】按冷站电量数据-下限" sheetId="3" r:id="rId2"/>
     <sheet name="全国主要城市气象情况" sheetId="2" r:id="rId3"/>
   </sheets>

--- a/00_sample/模板测算表/节能评估表-按冷站电量数据-二次泵版.xlsx
+++ b/00_sample/模板测算表/节能评估表-按冷站电量数据-二次泵版.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="15180"/>
+    <workbookView windowWidth="19200" windowHeight="9210" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="【1】按冷站电量数据-上限" sheetId="1" r:id="rId1"/>
-    <sheet name="【2】按冷站电量数据-下限" sheetId="3" r:id="rId2"/>
-    <sheet name="全国主要城市气象情况" sheetId="2" r:id="rId3"/>
+    <sheet name="【2】按冷站电量数据-下限" sheetId="2" r:id="rId2"/>
+    <sheet name="全国主要城市气象情况" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="71">
   <si>
     <t>节能量测算与评估表</t>
   </si>
@@ -171,27 +171,18 @@
     <t>冷却泵能耗占比</t>
   </si>
   <si>
-    <t>华南</t>
-  </si>
-  <si>
     <t>冷冻水额定温差（℃）</t>
   </si>
   <si>
     <t>冷冻泵能耗占比</t>
   </si>
   <si>
-    <t>华东</t>
-  </si>
-  <si>
     <t>冷冻泵最小频率（Hz）</t>
   </si>
   <si>
     <t>冷却塔能耗占比</t>
   </si>
   <si>
-    <t>华中</t>
-  </si>
-  <si>
     <t>冷机</t>
   </si>
   <si>
@@ -237,21 +228,12 @@
     <t>总计</t>
   </si>
   <si>
-    <t>西南</t>
-  </si>
-  <si>
     <t>冷机能耗（万kWh）</t>
   </si>
   <si>
-    <t>西北</t>
-  </si>
-  <si>
     <t>用户供水设定温度（℃）</t>
   </si>
   <si>
-    <t>华北</t>
-  </si>
-  <si>
     <t>预计供水温度（℃）</t>
   </si>
   <si>
@@ -358,6 +340,27 @@
   </si>
   <si>
     <t>济南</t>
+  </si>
+  <si>
+    <t>曼谷</t>
+  </si>
+  <si>
+    <t>罗勇</t>
+  </si>
+  <si>
+    <t>大城府</t>
+  </si>
+  <si>
+    <t>吉隆坡</t>
+  </si>
+  <si>
+    <t>槟城</t>
+  </si>
+  <si>
+    <t>胡志明市</t>
+  </si>
+  <si>
+    <t>北宁省</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1474,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1510,7 +1513,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="3" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="3" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1573,16 +1576,13 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1949,24 +1949,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:V30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="B1:R30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="2.38392857142857" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.38333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="30.25" style="1" customWidth="1"/>
-    <col min="4" max="9" width="9.63392857142857" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.3839285714286" style="1" customWidth="1"/>
+    <col min="4" max="9" width="9.63333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.3833333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="15" width="9.63392857142857" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.88392857142857" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.8928571428571" style="7" customWidth="1"/>
+    <col min="12" max="15" width="9.63333333333333" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.88333333333333" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.8916666666667" style="7" customWidth="1"/>
     <col min="18" max="21" width="9" style="1" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="12.8928571428571" style="7" customWidth="1"/>
+    <col min="22" max="22" width="12.8916666666667" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="7.5" customHeight="1"/>
-    <row r="2" ht="26.45" customHeight="1" spans="2:22">
+    <row r="2" ht="26.45" customHeight="1" spans="2:18">
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
@@ -1985,7 +1985,7 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" ht="26.45" customHeight="1" spans="2:22">
+    <row r="3" ht="26.45" customHeight="1" spans="2:18">
       <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
@@ -2013,11 +2013,8 @@
       <c r="P3" s="18">
         <v>0.58</v>
       </c>
-      <c r="Q3" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="26.45" customHeight="1" spans="2:22">
+    </row>
+    <row r="4" ht="26.45" customHeight="1" spans="2:18">
       <c r="B4" s="19"/>
       <c r="H4" s="20"/>
       <c r="I4" s="21"/>
@@ -2036,110 +2033,102 @@
       <c r="P4" s="18">
         <v>0.17</v>
       </c>
-      <c r="R4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" ht="26.45" customHeight="1" spans="2:22">
+      <c r="R4"/>
+    </row>
+    <row r="5" ht="26.45" customHeight="1" spans="2:18">
       <c r="B5" s="19"/>
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
       <c r="J5" s="15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="16"/>
       <c r="L5" s="17">
         <v>5</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N5" s="16"/>
       <c r="O5" s="14"/>
       <c r="P5" s="18">
         <v>0.2</v>
       </c>
-      <c r="R5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" ht="26.45" customHeight="1" spans="2:22">
+      <c r="R5"/>
+    </row>
+    <row r="6" ht="26.45" customHeight="1" spans="2:18">
       <c r="B6" s="19"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
       <c r="J6" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="20">
         <v>35</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="21"/>
       <c r="P6" s="26">
         <v>0.05</v>
       </c>
-      <c r="R6" t="s">
+      <c r="R6"/>
+    </row>
+    <row r="7" ht="21.95" customHeight="1" spans="2:18">
+      <c r="B7" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" ht="21.95" customHeight="1" spans="2:22">
-      <c r="B7" s="27" t="s">
+      <c r="E7" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="F7" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="G7" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="H7" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="I7" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="J7" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="K7" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="L7" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="M7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="28" t="s">
+      <c r="N7" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="28" t="s">
+      <c r="O7" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="28" t="s">
+      <c r="P7" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" ht="21.95" customHeight="1" spans="2:22">
+      <c r="R7"/>
+    </row>
+    <row r="8" ht="21.95" customHeight="1" spans="2:18">
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D8" s="32">
         <f t="shared" ref="D8:O8" si="0">D27*$P$3</f>
@@ -2193,14 +2182,12 @@
         <f>SUM(D8:O8)</f>
         <v>0</v>
       </c>
-      <c r="R8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" ht="21.95" customHeight="1" spans="2:22">
+      <c r="R8"/>
+    </row>
+    <row r="9" ht="21.95" customHeight="1" spans="2:18">
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="34"/>
@@ -2215,14 +2202,12 @@
       <c r="N9" s="34"/>
       <c r="O9" s="34"/>
       <c r="P9" s="33"/>
-      <c r="R9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" ht="21.95" customHeight="1" spans="2:22">
+      <c r="R9"/>
+    </row>
+    <row r="10" ht="21.95" customHeight="1" spans="2:18">
       <c r="B10" s="30"/>
       <c r="C10" s="31" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D10" s="35">
         <f>IF(D9&lt;8.5,D9+3.5,IF(D9&lt;10,D9+2.5,IF(D9&lt;12,D9+1.5,D9)))</f>
@@ -2245,15 +2230,15 @@
         <v>1.5</v>
       </c>
       <c r="I10" s="35">
-        <f t="shared" ref="I10:K10" si="1">IF(I9&lt;8.5,I9+1,IF(I9&lt;10,I9,IF(I9&lt;12,I9,I9)))</f>
+        <f>IF(I9&lt;8.5,I9+1,IF(I9&lt;10,I9,IF(I9&lt;12,I9,I9)))</f>
         <v>1</v>
       </c>
       <c r="J10" s="35">
-        <f t="shared" si="1"/>
+        <f>IF(J9&lt;8.5,J9+1,IF(J9&lt;10,J9,IF(J9&lt;12,J9,J9)))</f>
         <v>1</v>
       </c>
       <c r="K10" s="35">
-        <f t="shared" si="1"/>
+        <f>IF(K9&lt;8.5,K9+1,IF(K9&lt;10,K9,IF(K9&lt;12,K9,K9)))</f>
         <v>1</v>
       </c>
       <c r="L10" s="35">
@@ -2274,78 +2259,70 @@
       </c>
       <c r="P10" s="33"/>
     </row>
-    <row r="11" ht="21.95" customHeight="1" spans="2:22">
+    <row r="11" ht="21.95" customHeight="1" spans="2:18">
       <c r="B11" s="36"/>
       <c r="C11" s="37" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D11" s="38">
-        <f>MAX(D8*(D10-D9)*0.04,0)</f>
+        <f t="shared" ref="D11:O11" si="1">MAX(D8*(D10-D9)*0.04,0)</f>
         <v>0</v>
       </c>
       <c r="E11" s="38">
-        <f>MAX(E8*(E10-E9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F11" s="38">
-        <f>MAX(F8*(F10-F9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G11" s="38">
-        <f>MAX(G8*(G10-G9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H11" s="38">
-        <f>MAX(H8*(H10-H9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I11" s="38">
-        <f>MAX(I8*(I10-I9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J11" s="38">
-        <f>MAX(J8*(J10-J9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K11" s="38">
-        <f>MAX(K8*(K10-K9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L11" s="38">
-        <f>MAX(L8*(L10-L9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M11" s="38">
-        <f>MAX(M8*(M10-M9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N11" s="38">
-        <f>MAX(N8*(N10-N9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O11" s="38">
-        <f>MAX(O8*(O10-O9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P11" s="39">
         <f>MAX(SUM(D11:O11),0)</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="7" t="e">
-        <f>P11/P8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V11" s="7" t="e">
-        <f>P11/P27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" ht="21.95" customHeight="1" spans="2:22">
+    </row>
+    <row r="12" ht="21.95" customHeight="1" spans="2:18">
       <c r="B12" s="27" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D12" s="41">
         <f t="shared" ref="D12:O12" si="2">D27*$P$4</f>
@@ -2400,218 +2377,210 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="21.95" customHeight="1" spans="2:22">
+    <row r="13" ht="21.95" customHeight="1" spans="2:18">
       <c r="B13" s="30"/>
       <c r="C13" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
+        <v>32</v>
+      </c>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
       <c r="P13" s="33"/>
     </row>
-    <row r="14" ht="21.95" customHeight="1" spans="2:22">
+    <row r="14" ht="21.95" customHeight="1" spans="2:18">
       <c r="B14" s="30"/>
       <c r="C14" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
+        <v>33</v>
+      </c>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
       <c r="P14" s="33"/>
     </row>
-    <row r="15" ht="21.95" customHeight="1" spans="2:22">
+    <row r="15" ht="21.95" customHeight="1" spans="2:18">
       <c r="B15" s="30"/>
       <c r="C15" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="44">
+        <v>34</v>
+      </c>
+      <c r="D15" s="43">
         <f t="shared" ref="D15:O15" si="3">IF(D14&lt;=$L$3,IF(D14/$L$3*D13&lt;$L$4,$L$4,IF(D14/$L$3*D13&lt;=50,D14/$L$3*D13,50)),D13)</f>
         <v>35</v>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="J15" s="44">
+      <c r="J15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="K15" s="44">
+      <c r="K15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="L15" s="44">
+      <c r="L15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="M15" s="44">
+      <c r="M15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="N15" s="44">
+      <c r="N15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="O15" s="44">
+      <c r="O15" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="P15" s="33"/>
     </row>
-    <row r="16" ht="21.95" customHeight="1" spans="2:22">
+    <row r="16" ht="21.95" customHeight="1" spans="2:18">
       <c r="B16" s="36"/>
       <c r="C16" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="45" t="e">
-        <f>MAX(D12*(1-(D15/D13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E16" s="45" t="e">
-        <f>MAX(E12*(1-(E15/E13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" s="45" t="e">
-        <f>MAX(F12*(1-(F15/F13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G16" s="45" t="e">
-        <f>MAX(G12*(1-(G15/G13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H16" s="45" t="e">
-        <f>MAX(H12*(1-(H15/H13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I16" s="45" t="e">
-        <f>MAX(I12*(1-(I15/I13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J16" s="45" t="e">
-        <f>MAX(J12*(1-(J15/J13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K16" s="45" t="e">
-        <f>MAX(K12*(1-(K15/K13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L16" s="45" t="e">
-        <f>MAX(L12*(1-(L15/L13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M16" s="45" t="e">
-        <f>MAX(M12*(1-(M15/M13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N16" s="45" t="e">
-        <f>MAX(N12*(1-(N15/N13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O16" s="45" t="e">
-        <f>MAX(O12*(1-(O15/O13)^2.5),0)</f>
+        <v>35</v>
+      </c>
+      <c r="D16" s="44" t="e">
+        <f t="shared" ref="D16:O16" si="4">MAX(D12*(1-(D15/D13)^2.5),0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O16" s="44" t="e">
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P16" s="39" t="e">
         <f>MAX(SUM(D16:O16),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q16" s="7" t="e">
-        <f>P16/P12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V16" s="7" t="e">
-        <f>P16/P27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" ht="21.95" customHeight="1" spans="2:22">
+    </row>
+    <row r="17" ht="21.95" customHeight="1" spans="2:16">
       <c r="B17" s="27" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D17" s="41">
-        <f t="shared" ref="D17:O17" si="4">D27*$P$5</f>
+        <f t="shared" ref="D17:O17" si="5">D27*$P$5</f>
         <v>0</v>
       </c>
       <c r="E17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P17" s="42">
@@ -2619,218 +2588,210 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="21.95" customHeight="1" spans="2:22">
+    <row r="18" ht="21.95" customHeight="1" spans="2:16">
       <c r="B18" s="30"/>
       <c r="C18" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
+        <v>32</v>
+      </c>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
       <c r="P18" s="33"/>
     </row>
-    <row r="19" ht="21.95" customHeight="1" spans="2:22">
+    <row r="19" ht="21.95" customHeight="1" spans="2:16">
       <c r="B19" s="30"/>
       <c r="C19" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
       <c r="P19" s="33"/>
     </row>
-    <row r="20" ht="21.95" customHeight="1" spans="2:22">
+    <row r="20" ht="21.95" customHeight="1" spans="2:16">
       <c r="B20" s="30"/>
       <c r="C20" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="44">
-        <f t="shared" ref="D20:O20" si="5">IF(D19&lt;=$L$5,IF(D19/$L$5*D18&lt;$L$6,$L$6,IF(D19/$L$5*D18&lt;=50,D19/$L$5*D18,50)),D18)</f>
+        <v>34</v>
+      </c>
+      <c r="D20" s="43">
+        <f t="shared" ref="D20:O20" si="6">IF(D19&lt;=$L$5,IF(D19/$L$5*D18&lt;$L$6,$L$6,IF(D19/$L$5*D18&lt;=50,D19/$L$5*D18,50)),D18)</f>
         <v>35</v>
       </c>
-      <c r="E20" s="44">
-        <f t="shared" si="5"/>
+      <c r="E20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="F20" s="44">
-        <f t="shared" si="5"/>
+      <c r="F20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="G20" s="44">
-        <f t="shared" si="5"/>
+      <c r="G20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="H20" s="44">
-        <f t="shared" si="5"/>
+      <c r="H20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="I20" s="44">
-        <f t="shared" si="5"/>
+      <c r="I20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="J20" s="44">
-        <f t="shared" si="5"/>
+      <c r="J20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="K20" s="44">
-        <f t="shared" si="5"/>
+      <c r="K20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="L20" s="44">
-        <f t="shared" si="5"/>
+      <c r="L20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="M20" s="44">
-        <f t="shared" si="5"/>
+      <c r="M20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="N20" s="44">
-        <f t="shared" si="5"/>
+      <c r="N20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="O20" s="44">
-        <f t="shared" si="5"/>
+      <c r="O20" s="43">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
       <c r="P20" s="33"/>
     </row>
-    <row r="21" ht="21.95" customHeight="1" spans="2:22">
+    <row r="21" ht="21.95" customHeight="1" spans="2:16">
       <c r="B21" s="36"/>
       <c r="C21" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="45" t="e">
-        <f>MAX(D17*(1-(D20/D18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E21" s="45" t="e">
-        <f>MAX(E17*(1-(E20/E18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F21" s="45" t="e">
-        <f>MAX(F17*(1-(F20/F18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G21" s="45" t="e">
-        <f>MAX(G17*(1-(G20/G18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H21" s="45" t="e">
-        <f>MAX(H17*(1-(H20/H18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I21" s="45" t="e">
-        <f>MAX(I17*(1-(I20/I18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J21" s="45" t="e">
-        <f>MAX(J17*(1-(J20/J18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K21" s="45" t="e">
-        <f>MAX(K17*(1-(K20/K18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L21" s="45" t="e">
-        <f>MAX(L17*(1-(L20/L18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M21" s="45" t="e">
-        <f>MAX(M17*(1-(M20/M18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N21" s="45" t="e">
-        <f>MAX(N17*(1-(N20/N18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O21" s="45" t="e">
-        <f>MAX(O17*(1-(O20/O18)^2.5),0)</f>
+        <v>39</v>
+      </c>
+      <c r="D21" s="44" t="e">
+        <f t="shared" ref="D21:O21" si="7">MAX(D17*(1-(D20/D18)^2.5),0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O21" s="44" t="e">
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P21" s="39" t="e">
         <f>MAX(SUM(D21:O21),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q21" s="7" t="e">
-        <f>P21/P17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V21" s="7" t="e">
-        <f>P21/P27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="22" ht="21.95" customHeight="1" spans="2:22">
+    </row>
+    <row r="22" ht="21.95" customHeight="1" spans="2:16">
       <c r="B22" s="27" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D22" s="41">
-        <f t="shared" ref="D22:O22" si="6">D27*$P$6</f>
+        <f t="shared" ref="D22:O22" si="8">D27*$P$6</f>
         <v>0</v>
       </c>
       <c r="E22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P22" s="42">
@@ -2838,325 +2799,281 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="21.95" customHeight="1" spans="2:22">
+    <row r="23" ht="21.95" customHeight="1" spans="2:16">
       <c r="B23" s="30"/>
       <c r="C23" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
-      <c r="O23" s="46"/>
+        <v>42</v>
+      </c>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
       <c r="P23" s="33"/>
     </row>
-    <row r="24" ht="21.95" customHeight="1" spans="2:22">
+    <row r="24" ht="21.95" customHeight="1" spans="2:16">
       <c r="B24" s="30"/>
       <c r="C24" s="31" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!D6,IF($H$4="华东",全国主要城市气象情况!D10,IF($H$4="华中",全国主要城市气象情况!D14,IF($H$4="西南",全国主要城市气象情况!D18,IF($H$4="西北",全国主要城市气象情况!D22,IF($H$4="华北",全国主要城市气象情况!D26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!D6,IF($H$4="华东",全国主要城市气象情况!D10,IF($H$4="华中",全国主要城市气象情况!D14,IF($H$4="西南",全国主要城市气象情况!D18,IF($H$4="西北",全国主要城市气象情况!D22,IF($H$4="华北",全国主要城市气象情况!D26,IF($H$4="曼谷",全国主要城市气象情况!D30,IF($H$4="罗勇",全国主要城市气象情况!D34,IF($H$4="大城府",全国主要城市气象情况!D38,IF($H$4="吉隆坡",全国主要城市气象情况!D42,IF($H$4="槟城",全国主要城市气象情况!D46,IF($H$4="胡志明市",全国主要城市气象情况!D50,IF($H$4="北宁省",全国主要城市气象情况!D54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="E24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!E6,IF($H$4="华东",全国主要城市气象情况!E10,IF($H$4="华中",全国主要城市气象情况!E14,IF($H$4="西南",全国主要城市气象情况!E18,IF($H$4="西北",全国主要城市气象情况!E22,IF($H$4="华北",全国主要城市气象情况!E26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!E6,IF($H$4="华东",全国主要城市气象情况!E10,IF($H$4="华中",全国主要城市气象情况!E14,IF($H$4="西南",全国主要城市气象情况!E18,IF($H$4="西北",全国主要城市气象情况!E22,IF($H$4="华北",全国主要城市气象情况!E26,IF($H$4="曼谷",全国主要城市气象情况!E30,IF($H$4="罗勇",全国主要城市气象情况!E34,IF($H$4="大城府",全国主要城市气象情况!E38,IF($H$4="吉隆坡",全国主要城市气象情况!E42,IF($H$4="槟城",全国主要城市气象情况!E46,IF($H$4="胡志明市",全国主要城市气象情况!E50,IF($H$4="北宁省",全国主要城市气象情况!E54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="F24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!F6,IF($H$4="华东",全国主要城市气象情况!F10,IF($H$4="华中",全国主要城市气象情况!F14,IF($H$4="西南",全国主要城市气象情况!F18,IF($H$4="西北",全国主要城市气象情况!F22,IF($H$4="华北",全国主要城市气象情况!F26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!F6,IF($H$4="华东",全国主要城市气象情况!F10,IF($H$4="华中",全国主要城市气象情况!F14,IF($H$4="西南",全国主要城市气象情况!F18,IF($H$4="西北",全国主要城市气象情况!F22,IF($H$4="华北",全国主要城市气象情况!F26,IF($H$4="曼谷",全国主要城市气象情况!F30,IF($H$4="罗勇",全国主要城市气象情况!F34,IF($H$4="大城府",全国主要城市气象情况!F38,IF($H$4="吉隆坡",全国主要城市气象情况!F42,IF($H$4="槟城",全国主要城市气象情况!F46,IF($H$4="胡志明市",全国主要城市气象情况!F50,IF($H$4="北宁省",全国主要城市气象情况!F54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="G24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!G6,IF($H$4="华东",全国主要城市气象情况!G10,IF($H$4="华中",全国主要城市气象情况!G14,IF($H$4="西南",全国主要城市气象情况!G18,IF($H$4="西北",全国主要城市气象情况!G22,IF($H$4="华北",全国主要城市气象情况!G26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!G6,IF($H$4="华东",全国主要城市气象情况!G10,IF($H$4="华中",全国主要城市气象情况!G14,IF($H$4="西南",全国主要城市气象情况!G18,IF($H$4="西北",全国主要城市气象情况!G22,IF($H$4="华北",全国主要城市气象情况!G26,IF($H$4="曼谷",全国主要城市气象情况!G30,IF($H$4="罗勇",全国主要城市气象情况!G34,IF($H$4="大城府",全国主要城市气象情况!G38,IF($H$4="吉隆坡",全国主要城市气象情况!G42,IF($H$4="槟城",全国主要城市气象情况!G46,IF($H$4="胡志明市",全国主要城市气象情况!G50,IF($H$4="北宁省",全国主要城市气象情况!G54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="H24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!H6,IF($H$4="华东",全国主要城市气象情况!H10,IF($H$4="华中",全国主要城市气象情况!H14,IF($H$4="西南",全国主要城市气象情况!H18,IF($H$4="西北",全国主要城市气象情况!H22,IF($H$4="华北",全国主要城市气象情况!H26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!H6,IF($H$4="华东",全国主要城市气象情况!H10,IF($H$4="华中",全国主要城市气象情况!H14,IF($H$4="西南",全国主要城市气象情况!H18,IF($H$4="西北",全国主要城市气象情况!H22,IF($H$4="华北",全国主要城市气象情况!H26,IF($H$4="曼谷",全国主要城市气象情况!H30,IF($H$4="罗勇",全国主要城市气象情况!H34,IF($H$4="大城府",全国主要城市气象情况!H38,IF($H$4="吉隆坡",全国主要城市气象情况!H42,IF($H$4="槟城",全国主要城市气象情况!H46,IF($H$4="胡志明市",全国主要城市气象情况!H50,IF($H$4="北宁省",全国主要城市气象情况!H54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="I24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!I6,IF($H$4="华东",全国主要城市气象情况!I10,IF($H$4="华中",全国主要城市气象情况!I14,IF($H$4="西南",全国主要城市气象情况!I18,IF($H$4="西北",全国主要城市气象情况!I22,IF($H$4="华北",全国主要城市气象情况!I26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!I6,IF($H$4="华东",全国主要城市气象情况!I10,IF($H$4="华中",全国主要城市气象情况!I14,IF($H$4="西南",全国主要城市气象情况!I18,IF($H$4="西北",全国主要城市气象情况!I22,IF($H$4="华北",全国主要城市气象情况!I26,IF($H$4="曼谷",全国主要城市气象情况!I30,IF($H$4="罗勇",全国主要城市气象情况!I34,IF($H$4="大城府",全国主要城市气象情况!I38,IF($H$4="吉隆坡",全国主要城市气象情况!I42,IF($H$4="槟城",全国主要城市气象情况!I46,IF($H$4="胡志明市",全国主要城市气象情况!I50,IF($H$4="北宁省",全国主要城市气象情况!I54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="J24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!J6,IF($H$4="华东",全国主要城市气象情况!J10,IF($H$4="华中",全国主要城市气象情况!J14,IF($H$4="西南",全国主要城市气象情况!J18,IF($H$4="西北",全国主要城市气象情况!J22,IF($H$4="华北",全国主要城市气象情况!J26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!J6,IF($H$4="华东",全国主要城市气象情况!J10,IF($H$4="华中",全国主要城市气象情况!J14,IF($H$4="西南",全国主要城市气象情况!J18,IF($H$4="西北",全国主要城市气象情况!J22,IF($H$4="华北",全国主要城市气象情况!J26,IF($H$4="曼谷",全国主要城市气象情况!J30,IF($H$4="罗勇",全国主要城市气象情况!J34,IF($H$4="大城府",全国主要城市气象情况!J38,IF($H$4="吉隆坡",全国主要城市气象情况!J42,IF($H$4="槟城",全国主要城市气象情况!J46,IF($H$4="胡志明市",全国主要城市气象情况!J50,IF($H$4="北宁省",全国主要城市气象情况!J54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="K24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!K6,IF($H$4="华东",全国主要城市气象情况!K10,IF($H$4="华中",全国主要城市气象情况!K14,IF($H$4="西南",全国主要城市气象情况!K18,IF($H$4="西北",全国主要城市气象情况!K22,IF($H$4="华北",全国主要城市气象情况!K26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!K6,IF($H$4="华东",全国主要城市气象情况!K10,IF($H$4="华中",全国主要城市气象情况!K14,IF($H$4="西南",全国主要城市气象情况!K18,IF($H$4="西北",全国主要城市气象情况!K22,IF($H$4="华北",全国主要城市气象情况!K26,IF($H$4="曼谷",全国主要城市气象情况!K30,IF($H$4="罗勇",全国主要城市气象情况!K34,IF($H$4="大城府",全国主要城市气象情况!K38,IF($H$4="吉隆坡",全国主要城市气象情况!K42,IF($H$4="槟城",全国主要城市气象情况!K46,IF($H$4="胡志明市",全国主要城市气象情况!K50,IF($H$4="北宁省",全国主要城市气象情况!K54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="L24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!L6,IF($H$4="华东",全国主要城市气象情况!L10,IF($H$4="华中",全国主要城市气象情况!L14,IF($H$4="西南",全国主要城市气象情况!L18,IF($H$4="西北",全国主要城市气象情况!L22,IF($H$4="华北",全国主要城市气象情况!L26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!L6,IF($H$4="华东",全国主要城市气象情况!L10,IF($H$4="华中",全国主要城市气象情况!L14,IF($H$4="西南",全国主要城市气象情况!L18,IF($H$4="西北",全国主要城市气象情况!L22,IF($H$4="华北",全国主要城市气象情况!L26,IF($H$4="曼谷",全国主要城市气象情况!L30,IF($H$4="罗勇",全国主要城市气象情况!L34,IF($H$4="大城府",全国主要城市气象情况!L38,IF($H$4="吉隆坡",全国主要城市气象情况!L42,IF($H$4="槟城",全国主要城市气象情况!L46,IF($H$4="胡志明市",全国主要城市气象情况!L50,IF($H$4="北宁省",全国主要城市气象情况!L54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="M24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!M6,IF($H$4="华东",全国主要城市气象情况!M10,IF($H$4="华中",全国主要城市气象情况!M14,IF($H$4="西南",全国主要城市气象情况!M18,IF($H$4="西北",全国主要城市气象情况!M22,IF($H$4="华北",全国主要城市气象情况!M26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!M6,IF($H$4="华东",全国主要城市气象情况!M10,IF($H$4="华中",全国主要城市气象情况!M14,IF($H$4="西南",全国主要城市气象情况!M18,IF($H$4="西北",全国主要城市气象情况!M22,IF($H$4="华北",全国主要城市气象情况!M26,IF($H$4="曼谷",全国主要城市气象情况!M30,IF($H$4="罗勇",全国主要城市气象情况!M34,IF($H$4="大城府",全国主要城市气象情况!M38,IF($H$4="吉隆坡",全国主要城市气象情况!M42,IF($H$4="槟城",全国主要城市气象情况!M46,IF($H$4="胡志明市",全国主要城市气象情况!M50,IF($H$4="北宁省",全国主要城市气象情况!M54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="N24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!N6,IF($H$4="华东",全国主要城市气象情况!N10,IF($H$4="华中",全国主要城市气象情况!N14,IF($H$4="西南",全国主要城市气象情况!N18,IF($H$4="西北",全国主要城市气象情况!N22,IF($H$4="华北",全国主要城市气象情况!N26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!N6,IF($H$4="华东",全国主要城市气象情况!N10,IF($H$4="华中",全国主要城市气象情况!N14,IF($H$4="西南",全国主要城市气象情况!N18,IF($H$4="西北",全国主要城市气象情况!N22,IF($H$4="华北",全国主要城市气象情况!N26,IF($H$4="曼谷",全国主要城市气象情况!N30,IF($H$4="罗勇",全国主要城市气象情况!N34,IF($H$4="大城府",全国主要城市气象情况!N38,IF($H$4="吉隆坡",全国主要城市气象情况!N42,IF($H$4="槟城",全国主要城市气象情况!N46,IF($H$4="胡志明市",全国主要城市气象情况!N50,IF($H$4="北宁省",全国主要城市气象情况!N54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="O24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!O6,IF($H$4="华东",全国主要城市气象情况!O10,IF($H$4="华中",全国主要城市气象情况!O14,IF($H$4="西南",全国主要城市气象情况!O18,IF($H$4="西北",全国主要城市气象情况!O22,IF($H$4="华北",全国主要城市气象情况!O26,0))))))+0.5</f>
-        <v>0.5</v>
+        <f>IF($H$4="华南",全国主要城市气象情况!O6,IF($H$4="华东",全国主要城市气象情况!O10,IF($H$4="华中",全国主要城市气象情况!O14,IF($H$4="西南",全国主要城市气象情况!O18,IF($H$4="西北",全国主要城市气象情况!O22,IF($H$4="华北",全国主要城市气象情况!O26,IF($H$4="曼谷",全国主要城市气象情况!O30,IF($H$4="罗勇",全国主要城市气象情况!O34,IF($H$4="大城府",全国主要城市气象情况!O38,IF($H$4="吉隆坡",全国主要城市气象情况!O42,IF($H$4="槟城",全国主要城市气象情况!O46,IF($H$4="胡志明市",全国主要城市气象情况!O50,IF($H$4="北宁省",全国主要城市气象情况!O54,0)))))))))))))</f>
+        <v>0</v>
       </c>
       <c r="P24" s="33"/>
     </row>
-    <row r="25" ht="21.95" customHeight="1" spans="2:22">
+    <row r="25" ht="21.95" customHeight="1" spans="2:16">
       <c r="B25" s="36"/>
-      <c r="C25" s="47" t="s">
-        <v>50</v>
+      <c r="C25" s="46" t="s">
+        <v>44</v>
       </c>
       <c r="D25" s="38">
-        <f>MAX(IF(D24&lt;D23,D8*0.015*(D23-D24),0))</f>
+        <f t="shared" ref="D25:O25" si="9">MAX(IF(D24&lt;D23,D8*0.015*(D23-D24),0))</f>
         <v>0</v>
       </c>
       <c r="E25" s="38">
-        <f>MAX(IF(E24&lt;E23,E8*0.015*(E23-E24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F25" s="38">
-        <f>MAX(IF(F24&lt;F23,F8*0.015*(F23-F24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G25" s="38">
-        <f>MAX(IF(G24&lt;G23,G8*0.015*(G23-G24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H25" s="38">
-        <f>MAX(IF(H24&lt;H23,H8*0.015*(H23-H24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I25" s="38">
-        <f>MAX(IF(I24&lt;I23,I8*0.015*(I23-I24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J25" s="38">
-        <f>MAX(IF(J24&lt;J23,J8*0.015*(J23-J24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K25" s="38">
-        <f>MAX(IF(K24&lt;K23,K8*0.015*(K23-K24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L25" s="38">
-        <f>MAX(IF(L24&lt;L23,L8*0.015*(L23-L24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M25" s="38">
-        <f>MAX(IF(M24&lt;M23,M8*0.015*(M23-M24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N25" s="38">
-        <f>MAX(IF(N24&lt;N23,N8*0.015*(N23-N24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O25" s="38">
-        <f>MAX(IF(O24&lt;O23,O8*0.015*(O23-O24),0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P25" s="39">
         <f>MAX(SUM(D25:O25),0)</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="7" t="e">
-        <f>P25/P8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V25" s="7" t="e">
-        <f>P25/P27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="26" ht="6" customHeight="1" spans="2:22">
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="51"/>
-    </row>
-    <row r="27" ht="21.95" customHeight="1" spans="2:22">
-      <c r="B27" s="52" t="s">
-        <v>51</v>
+    </row>
+    <row r="26" ht="6" customHeight="1" spans="2:16">
+      <c r="B26" s="47"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="50"/>
+    </row>
+    <row r="27" ht="21.95" customHeight="1" spans="2:16">
+      <c r="B27" s="51" t="s">
+        <v>45</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="54">
+        <v>46</v>
+      </c>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="52"/>
+      <c r="P27" s="53">
         <f>SUM(D27:O27)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="21.95" customHeight="1" spans="2:22">
+    <row r="28" ht="21.95" customHeight="1" spans="2:16">
       <c r="B28" s="30"/>
       <c r="C28" s="31" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D28" s="32" t="e">
-        <f t="shared" ref="D28:O28" si="7">D11+D16+D21+D25</f>
+        <f t="shared" ref="D28:O28" si="10">D11+D16+D21+D25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" s="32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F28" s="32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H28" s="32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J28" s="32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K28" s="32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L28" s="32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M28" s="32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N28" s="32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O28" s="32" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P28" s="54" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P28" s="53" t="e">
         <f>SUM(D28:O28)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" ht="21.95" customHeight="1" spans="2:22">
+    <row r="29" ht="21.95" customHeight="1" spans="2:16">
       <c r="B29" s="36"/>
       <c r="C29" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="55" t="e">
+        <v>48</v>
+      </c>
+      <c r="D29" s="54" t="e">
         <f>P28/P27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E29" s="56"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="H29" s="57"/>
-      <c r="I29" s="59">
+      <c r="E29" s="55"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" s="56"/>
+      <c r="I29" s="58">
         <v>0.8</v>
       </c>
-      <c r="J29" s="56"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="M29" s="56"/>
-      <c r="N29" s="61" t="e">
+      <c r="J29" s="55"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="55"/>
+      <c r="N29" s="60" t="e">
         <f>P28*I29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="56"/>
-      <c r="P29" s="62"/>
-    </row>
-    <row r="30" spans="2:22">
-      <c r="D30" s="63" t="e">
-        <f t="shared" ref="D30:O30" si="8">D28/D27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O30" s="63" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="O29" s="55"/>
+      <c r="P29" s="61"/>
+    </row>
+    <row r="30" spans="2:16">
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -3198,24 +3115,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:V30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="B1:R30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="2.38392857142857" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.38333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="30.25" style="1" customWidth="1"/>
-    <col min="4" max="9" width="9.63392857142857" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.3839285714286" style="1" customWidth="1"/>
+    <col min="4" max="9" width="9.63333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.3833333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="15" width="9.63392857142857" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.88392857142857" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.8928571428571" style="7" customWidth="1"/>
+    <col min="12" max="15" width="9.63333333333333" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.88333333333333" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.8916666666667" style="7" customWidth="1"/>
     <col min="18" max="21" width="9" style="1" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="12.8928571428571" style="7" customWidth="1"/>
+    <col min="22" max="22" width="12.8916666666667" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="7.5" customHeight="1"/>
-    <row r="2" ht="26.45" customHeight="1" spans="2:22">
+    <row r="2" ht="26.45" customHeight="1" spans="2:18">
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
@@ -3234,7 +3151,7 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" ht="26.45" customHeight="1" spans="2:22">
+    <row r="3" ht="26.45" customHeight="1" spans="2:18">
       <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
@@ -3262,17 +3179,9 @@
       <c r="P3" s="18">
         <v>0.6</v>
       </c>
-      <c r="Q3" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="26.45" customHeight="1" spans="2:22">
+    </row>
+    <row r="4" ht="26.45" customHeight="1" spans="2:18">
       <c r="B4" s="19"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
       <c r="H4" s="20"/>
       <c r="I4" s="21"/>
       <c r="J4" s="15" t="s">
@@ -3290,120 +3199,102 @@
       <c r="P4" s="18">
         <v>0.15</v>
       </c>
-      <c r="R4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" ht="26.45" customHeight="1" spans="2:22">
+      <c r="R4"/>
+    </row>
+    <row r="5" ht="26.45" customHeight="1" spans="2:18">
       <c r="B5" s="19"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
       <c r="J5" s="15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="16"/>
       <c r="L5" s="17">
         <v>5</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N5" s="16"/>
       <c r="O5" s="14"/>
       <c r="P5" s="18">
         <v>0.2</v>
       </c>
-      <c r="R5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" ht="26.45" customHeight="1" spans="2:22">
+      <c r="R5"/>
+    </row>
+    <row r="6" ht="26.45" customHeight="1" spans="2:18">
       <c r="B6" s="19"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
       <c r="J6" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="20">
         <v>38</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="21"/>
       <c r="P6" s="26">
         <v>0.05</v>
       </c>
-      <c r="R6" t="s">
+      <c r="R6"/>
+    </row>
+    <row r="7" ht="21.95" customHeight="1" spans="2:18">
+      <c r="B7" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" ht="21.95" customHeight="1" spans="2:22">
-      <c r="B7" s="27" t="s">
+      <c r="E7" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="F7" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="G7" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="H7" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="I7" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="J7" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="K7" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="L7" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="M7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="28" t="s">
+      <c r="N7" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="28" t="s">
+      <c r="O7" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="28" t="s">
+      <c r="P7" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" ht="21.95" customHeight="1" spans="2:22">
+      <c r="R7"/>
+    </row>
+    <row r="8" ht="21.95" customHeight="1" spans="2:18">
       <c r="B8" s="30"/>
       <c r="C8" s="31" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D8" s="32">
         <f t="shared" ref="D8:O8" si="0">D27*$P$3</f>
@@ -3454,17 +3345,15 @@
         <v>0</v>
       </c>
       <c r="P8" s="33">
-        <f t="shared" ref="P8:P12" si="1">SUM(D8:O8)</f>
-        <v>0</v>
-      </c>
-      <c r="R8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" ht="21.95" customHeight="1" spans="2:22">
+        <f>SUM(D8:O8)</f>
+        <v>0</v>
+      </c>
+      <c r="R8"/>
+    </row>
+    <row r="9" ht="21.95" customHeight="1" spans="2:18">
       <c r="B9" s="30"/>
       <c r="C9" s="31" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="34"/>
@@ -3479,14 +3368,12 @@
       <c r="N9" s="34"/>
       <c r="O9" s="34"/>
       <c r="P9" s="33"/>
-      <c r="R9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" ht="21.95" customHeight="1" spans="2:22">
+      <c r="R9"/>
+    </row>
+    <row r="10" ht="21.95" customHeight="1" spans="2:18">
       <c r="B10" s="30"/>
       <c r="C10" s="31" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D10" s="35">
         <f>IF(D9&lt;8.5,D9+3,IF(D9&lt;10,D9+2,IF(D9&lt;12,D9+1,D9)))</f>
@@ -3538,78 +3425,70 @@
       </c>
       <c r="P10" s="33"/>
     </row>
-    <row r="11" ht="21.95" customHeight="1" spans="2:22">
+    <row r="11" ht="21.95" customHeight="1" spans="2:18">
       <c r="B11" s="36"/>
       <c r="C11" s="37" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D11" s="38">
-        <f>MAX(D8*(D10-D9)*0.04,0)</f>
+        <f t="shared" ref="D11:O11" si="1">MAX(D8*(D10-D9)*0.04,0)</f>
         <v>0</v>
       </c>
       <c r="E11" s="38">
-        <f>MAX(E8*(E10-E9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F11" s="38">
-        <f>MAX(F8*(F10-F9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G11" s="38">
-        <f>MAX(G8*(G10-G9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H11" s="38">
-        <f>MAX(H8*(H10-H9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I11" s="38">
-        <f>MAX(I8*(I10-I9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J11" s="38">
-        <f>MAX(J8*(J10-J9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K11" s="38">
-        <f>MAX(K8*(K10-K9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L11" s="38">
-        <f>MAX(L8*(L10-L9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M11" s="38">
-        <f>MAX(M8*(M10-M9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N11" s="38">
-        <f>MAX(N8*(N10-N9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O11" s="38">
-        <f>MAX(O8*(O10-O9)*0.04,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P11" s="39">
         <f>MAX(SUM(D11:O11),0)</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="7" t="e">
-        <f>P11/P8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V11" s="7" t="e">
-        <f>P11/P27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" ht="21.95" customHeight="1" spans="2:22">
+    </row>
+    <row r="12" ht="21.95" customHeight="1" spans="2:18">
       <c r="B12" s="27" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D12" s="41">
         <f t="shared" ref="D12:O12" si="2">D27*$P$4</f>
@@ -3660,222 +3539,214 @@
         <v>0</v>
       </c>
       <c r="P12" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="21.95" customHeight="1" spans="2:22">
+        <f>SUM(D12:O12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="21.95" customHeight="1" spans="2:18">
       <c r="B13" s="30"/>
       <c r="C13" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
+        <v>32</v>
+      </c>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
       <c r="P13" s="33"/>
     </row>
-    <row r="14" ht="21.95" customHeight="1" spans="2:22">
+    <row r="14" ht="21.95" customHeight="1" spans="2:18">
       <c r="B14" s="30"/>
       <c r="C14" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
+        <v>33</v>
+      </c>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
       <c r="P14" s="33"/>
     </row>
-    <row r="15" ht="21.95" customHeight="1" spans="2:22">
+    <row r="15" ht="21.95" customHeight="1" spans="2:18">
       <c r="B15" s="30"/>
       <c r="C15" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="44">
+        <v>34</v>
+      </c>
+      <c r="D15" s="43">
         <f t="shared" ref="D15:O15" si="3">IF(D14&lt;=$L$3,IF(D14/$L$3*D13&lt;$L$4,$L$4,IF(D14/$L$3*D13&lt;=50,D14/$L$3*D13,50)),D13)</f>
         <v>38</v>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="J15" s="44">
+      <c r="J15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="K15" s="44">
+      <c r="K15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="L15" s="44">
+      <c r="L15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="M15" s="44">
+      <c r="M15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="N15" s="44">
+      <c r="N15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="O15" s="44">
+      <c r="O15" s="43">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="P15" s="33"/>
     </row>
-    <row r="16" ht="21.95" customHeight="1" spans="2:22">
+    <row r="16" ht="21.95" customHeight="1" spans="2:18">
       <c r="B16" s="36"/>
       <c r="C16" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="45" t="e">
-        <f>MAX(D12*(1-(D15/D13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E16" s="45" t="e">
-        <f>MAX(E12*(1-(E15/E13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" s="45" t="e">
-        <f>MAX(F12*(1-(F15/F13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G16" s="45" t="e">
-        <f>MAX(G12*(1-(G15/G13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H16" s="45" t="e">
-        <f>MAX(H12*(1-(H15/H13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I16" s="45" t="e">
-        <f>MAX(I12*(1-(I15/I13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J16" s="45" t="e">
-        <f>MAX(J12*(1-(J15/J13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K16" s="45" t="e">
-        <f>MAX(K12*(1-(K15/K13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L16" s="45" t="e">
-        <f>MAX(L12*(1-(L15/L13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M16" s="45" t="e">
-        <f>MAX(M12*(1-(M15/M13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N16" s="45" t="e">
-        <f>MAX(N12*(1-(N15/N13)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O16" s="45" t="e">
-        <f>MAX(O12*(1-(O15/O13)^2.5),0)</f>
+        <v>35</v>
+      </c>
+      <c r="D16" s="44" t="e">
+        <f t="shared" ref="D16:O16" si="4">MAX(D12*(1-(D15/D13)^2.5),0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N16" s="44" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O16" s="44" t="e">
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P16" s="39" t="e">
         <f>MAX(SUM(D16:O16),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q16" s="7" t="e">
-        <f>P16/P12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V16" s="7" t="e">
-        <f>P16/P27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" ht="21.95" customHeight="1" spans="2:22">
+    </row>
+    <row r="17" ht="21.95" customHeight="1" spans="2:16">
       <c r="B17" s="27" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D17" s="41">
-        <f t="shared" ref="D17:O17" si="4">D27*$P$5</f>
+        <f t="shared" ref="D17:O17" si="5">D27*$P$5</f>
         <v>0</v>
       </c>
       <c r="E17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P17" s="42">
@@ -3883,218 +3754,210 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="21.95" customHeight="1" spans="2:22">
+    <row r="18" ht="21.95" customHeight="1" spans="2:16">
       <c r="B18" s="30"/>
       <c r="C18" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
+        <v>32</v>
+      </c>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
       <c r="P18" s="33"/>
     </row>
-    <row r="19" ht="21.95" customHeight="1" spans="2:22">
+    <row r="19" ht="21.95" customHeight="1" spans="2:16">
       <c r="B19" s="30"/>
       <c r="C19" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
       <c r="P19" s="33"/>
     </row>
-    <row r="20" ht="21.95" customHeight="1" spans="2:22">
+    <row r="20" ht="21.95" customHeight="1" spans="2:16">
       <c r="B20" s="30"/>
       <c r="C20" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="44">
-        <f t="shared" ref="D20:O20" si="5">IF(D19&lt;=$L$5,IF(D19/$L$5*D18&lt;$L$6,$L$6,IF(D19/$L$5*D18&lt;=50,D19/$L$5*D18,50)),D18)</f>
+        <v>34</v>
+      </c>
+      <c r="D20" s="43">
+        <f t="shared" ref="D20:O20" si="6">IF(D19&lt;=$L$5,IF(D19/$L$5*D18&lt;$L$6,$L$6,IF(D19/$L$5*D18&lt;=50,D19/$L$5*D18,50)),D18)</f>
         <v>38</v>
       </c>
-      <c r="E20" s="44">
-        <f t="shared" si="5"/>
+      <c r="E20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="F20" s="44">
-        <f t="shared" si="5"/>
+      <c r="F20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="G20" s="44">
-        <f t="shared" si="5"/>
+      <c r="G20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="H20" s="44">
-        <f t="shared" si="5"/>
+      <c r="H20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="I20" s="44">
-        <f t="shared" si="5"/>
+      <c r="I20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="J20" s="44">
-        <f t="shared" si="5"/>
+      <c r="J20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="K20" s="44">
-        <f t="shared" si="5"/>
+      <c r="K20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="L20" s="44">
-        <f t="shared" si="5"/>
+      <c r="L20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="M20" s="44">
-        <f t="shared" si="5"/>
+      <c r="M20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="N20" s="44">
-        <f t="shared" si="5"/>
+      <c r="N20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="O20" s="44">
-        <f t="shared" si="5"/>
+      <c r="O20" s="43">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
       <c r="P20" s="33"/>
     </row>
-    <row r="21" ht="21.95" customHeight="1" spans="2:22">
+    <row r="21" ht="21.95" customHeight="1" spans="2:16">
       <c r="B21" s="36"/>
       <c r="C21" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="45" t="e">
-        <f>MAX(D17*(1-(D20/D18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E21" s="45" t="e">
-        <f>MAX(E17*(1-(E20/E18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F21" s="45" t="e">
-        <f>MAX(F17*(1-(F20/F18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G21" s="45" t="e">
-        <f>MAX(G17*(1-(G20/G18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H21" s="45" t="e">
-        <f>MAX(H17*(1-(H20/H18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I21" s="45" t="e">
-        <f>MAX(I17*(1-(I20/I18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J21" s="45" t="e">
-        <f>MAX(J17*(1-(J20/J18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K21" s="45" t="e">
-        <f>MAX(K17*(1-(K20/K18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L21" s="45" t="e">
-        <f>MAX(L17*(1-(L20/L18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M21" s="45" t="e">
-        <f>MAX(M17*(1-(M20/M18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N21" s="45" t="e">
-        <f>MAX(N17*(1-(N20/N18)^2.5),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O21" s="45" t="e">
-        <f>MAX(O17*(1-(O20/O18)^2.5),0)</f>
+        <v>39</v>
+      </c>
+      <c r="D21" s="44" t="e">
+        <f t="shared" ref="D21:O21" si="7">MAX(D17*(1-(D20/D18)^2.5),0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N21" s="44" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O21" s="44" t="e">
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P21" s="39" t="e">
         <f>MAX(SUM(D21:O21),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q21" s="7" t="e">
-        <f>P21/P17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V21" s="7" t="e">
-        <f>P21/P27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="22" ht="21.95" customHeight="1" spans="2:22">
+    </row>
+    <row r="22" ht="21.95" customHeight="1" spans="2:16">
       <c r="B22" s="27" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D22" s="41">
-        <f t="shared" ref="D22:O22" si="6">D27*$P$6</f>
+        <f t="shared" ref="D22:O22" si="8">D27*$P$6</f>
         <v>0</v>
       </c>
       <c r="E22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O22" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P22" s="42">
@@ -4102,325 +3965,281 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="21.95" customHeight="1" spans="2:22">
+    <row r="23" ht="21.95" customHeight="1" spans="2:16">
       <c r="B23" s="30"/>
       <c r="C23" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
-      <c r="O23" s="46"/>
+        <v>42</v>
+      </c>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
       <c r="P23" s="33"/>
     </row>
-    <row r="24" ht="21.95" customHeight="1" spans="2:22">
+    <row r="24" ht="21.95" customHeight="1" spans="2:16">
       <c r="B24" s="30"/>
       <c r="C24" s="31" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!D6,IF($H$4="华东",全国主要城市气象情况!D10,IF($H$4="华中",全国主要城市气象情况!D14,IF($H$4="西南",全国主要城市气象情况!D18,IF($H$4="西北",全国主要城市气象情况!D22,IF($H$4="华北",全国主要城市气象情况!D26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!D6,IF($H$4="华东",全国主要城市气象情况!D10,IF($H$4="华中",全国主要城市气象情况!D14,IF($H$4="西南",全国主要城市气象情况!D18,IF($H$4="西北",全国主要城市气象情况!D22,IF($H$4="华北",全国主要城市气象情况!D26,IF($H$4="曼谷",全国主要城市气象情况!D30,IF($H$4="罗勇",全国主要城市气象情况!D34,IF($H$4="大城府",全国主要城市气象情况!D38,IF($H$4="吉隆坡",全国主要城市气象情况!D42,IF($H$4="槟城",全国主要城市气象情况!D46,IF($H$4="胡志明市",全国主要城市气象情况!D50,IF($H$4="北宁省",全国主要城市气象情况!D54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="E24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!E6,IF($H$4="华东",全国主要城市气象情况!E10,IF($H$4="华中",全国主要城市气象情况!E14,IF($H$4="西南",全国主要城市气象情况!E18,IF($H$4="西北",全国主要城市气象情况!E22,IF($H$4="华北",全国主要城市气象情况!E26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!E6,IF($H$4="华东",全国主要城市气象情况!E10,IF($H$4="华中",全国主要城市气象情况!E14,IF($H$4="西南",全国主要城市气象情况!E18,IF($H$4="西北",全国主要城市气象情况!E22,IF($H$4="华北",全国主要城市气象情况!E26,IF($H$4="曼谷",全国主要城市气象情况!E30,IF($H$4="罗勇",全国主要城市气象情况!E34,IF($H$4="大城府",全国主要城市气象情况!E38,IF($H$4="吉隆坡",全国主要城市气象情况!E42,IF($H$4="槟城",全国主要城市气象情况!E46,IF($H$4="胡志明市",全国主要城市气象情况!E50,IF($H$4="北宁省",全国主要城市气象情况!E54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="F24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!F6,IF($H$4="华东",全国主要城市气象情况!F10,IF($H$4="华中",全国主要城市气象情况!F14,IF($H$4="西南",全国主要城市气象情况!F18,IF($H$4="西北",全国主要城市气象情况!F22,IF($H$4="华北",全国主要城市气象情况!F26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!F6,IF($H$4="华东",全国主要城市气象情况!F10,IF($H$4="华中",全国主要城市气象情况!F14,IF($H$4="西南",全国主要城市气象情况!F18,IF($H$4="西北",全国主要城市气象情况!F22,IF($H$4="华北",全国主要城市气象情况!F26,IF($H$4="曼谷",全国主要城市气象情况!F30,IF($H$4="罗勇",全国主要城市气象情况!F34,IF($H$4="大城府",全国主要城市气象情况!F38,IF($H$4="吉隆坡",全国主要城市气象情况!F42,IF($H$4="槟城",全国主要城市气象情况!F46,IF($H$4="胡志明市",全国主要城市气象情况!F50,IF($H$4="北宁省",全国主要城市气象情况!F54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="G24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!G6,IF($H$4="华东",全国主要城市气象情况!G10,IF($H$4="华中",全国主要城市气象情况!G14,IF($H$4="西南",全国主要城市气象情况!G18,IF($H$4="西北",全国主要城市气象情况!G22,IF($H$4="华北",全国主要城市气象情况!G26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!G6,IF($H$4="华东",全国主要城市气象情况!G10,IF($H$4="华中",全国主要城市气象情况!G14,IF($H$4="西南",全国主要城市气象情况!G18,IF($H$4="西北",全国主要城市气象情况!G22,IF($H$4="华北",全国主要城市气象情况!G26,IF($H$4="曼谷",全国主要城市气象情况!G30,IF($H$4="罗勇",全国主要城市气象情况!G34,IF($H$4="大城府",全国主要城市气象情况!G38,IF($H$4="吉隆坡",全国主要城市气象情况!G42,IF($H$4="槟城",全国主要城市气象情况!G46,IF($H$4="胡志明市",全国主要城市气象情况!G50,IF($H$4="北宁省",全国主要城市气象情况!G54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="H24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!H6,IF($H$4="华东",全国主要城市气象情况!H10,IF($H$4="华中",全国主要城市气象情况!H14,IF($H$4="西南",全国主要城市气象情况!H18,IF($H$4="西北",全国主要城市气象情况!H22,IF($H$4="华北",全国主要城市气象情况!H26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!H6,IF($H$4="华东",全国主要城市气象情况!H10,IF($H$4="华中",全国主要城市气象情况!H14,IF($H$4="西南",全国主要城市气象情况!H18,IF($H$4="西北",全国主要城市气象情况!H22,IF($H$4="华北",全国主要城市气象情况!H26,IF($H$4="曼谷",全国主要城市气象情况!H30,IF($H$4="罗勇",全国主要城市气象情况!H34,IF($H$4="大城府",全国主要城市气象情况!H38,IF($H$4="吉隆坡",全国主要城市气象情况!H42,IF($H$4="槟城",全国主要城市气象情况!H46,IF($H$4="胡志明市",全国主要城市气象情况!H50,IF($H$4="北宁省",全国主要城市气象情况!H54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="I24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!I6,IF($H$4="华东",全国主要城市气象情况!I10,IF($H$4="华中",全国主要城市气象情况!I14,IF($H$4="西南",全国主要城市气象情况!I18,IF($H$4="西北",全国主要城市气象情况!I22,IF($H$4="华北",全国主要城市气象情况!I26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!I6,IF($H$4="华东",全国主要城市气象情况!I10,IF($H$4="华中",全国主要城市气象情况!I14,IF($H$4="西南",全国主要城市气象情况!I18,IF($H$4="西北",全国主要城市气象情况!I22,IF($H$4="华北",全国主要城市气象情况!I26,IF($H$4="曼谷",全国主要城市气象情况!I30,IF($H$4="罗勇",全国主要城市气象情况!I34,IF($H$4="大城府",全国主要城市气象情况!I38,IF($H$4="吉隆坡",全国主要城市气象情况!I42,IF($H$4="槟城",全国主要城市气象情况!I46,IF($H$4="胡志明市",全国主要城市气象情况!I50,IF($H$4="北宁省",全国主要城市气象情况!I54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="J24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!J6,IF($H$4="华东",全国主要城市气象情况!J10,IF($H$4="华中",全国主要城市气象情况!J14,IF($H$4="西南",全国主要城市气象情况!J18,IF($H$4="西北",全国主要城市气象情况!J22,IF($H$4="华北",全国主要城市气象情况!J26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!J6,IF($H$4="华东",全国主要城市气象情况!J10,IF($H$4="华中",全国主要城市气象情况!J14,IF($H$4="西南",全国主要城市气象情况!J18,IF($H$4="西北",全国主要城市气象情况!J22,IF($H$4="华北",全国主要城市气象情况!J26,IF($H$4="曼谷",全国主要城市气象情况!J30,IF($H$4="罗勇",全国主要城市气象情况!J34,IF($H$4="大城府",全国主要城市气象情况!J38,IF($H$4="吉隆坡",全国主要城市气象情况!J42,IF($H$4="槟城",全国主要城市气象情况!J46,IF($H$4="胡志明市",全国主要城市气象情况!J50,IF($H$4="北宁省",全国主要城市气象情况!J54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="K24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!K6,IF($H$4="华东",全国主要城市气象情况!K10,IF($H$4="华中",全国主要城市气象情况!K14,IF($H$4="西南",全国主要城市气象情况!K18,IF($H$4="西北",全国主要城市气象情况!K22,IF($H$4="华北",全国主要城市气象情况!K26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!K6,IF($H$4="华东",全国主要城市气象情况!K10,IF($H$4="华中",全国主要城市气象情况!K14,IF($H$4="西南",全国主要城市气象情况!K18,IF($H$4="西北",全国主要城市气象情况!K22,IF($H$4="华北",全国主要城市气象情况!K26,IF($H$4="曼谷",全国主要城市气象情况!K30,IF($H$4="罗勇",全国主要城市气象情况!K34,IF($H$4="大城府",全国主要城市气象情况!K38,IF($H$4="吉隆坡",全国主要城市气象情况!K42,IF($H$4="槟城",全国主要城市气象情况!K46,IF($H$4="胡志明市",全国主要城市气象情况!K50,IF($H$4="北宁省",全国主要城市气象情况!K54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="L24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!L6,IF($H$4="华东",全国主要城市气象情况!L10,IF($H$4="华中",全国主要城市气象情况!L14,IF($H$4="西南",全国主要城市气象情况!L18,IF($H$4="西北",全国主要城市气象情况!L22,IF($H$4="华北",全国主要城市气象情况!L26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!L6,IF($H$4="华东",全国主要城市气象情况!L10,IF($H$4="华中",全国主要城市气象情况!L14,IF($H$4="西南",全国主要城市气象情况!L18,IF($H$4="西北",全国主要城市气象情况!L22,IF($H$4="华北",全国主要城市气象情况!L26,IF($H$4="曼谷",全国主要城市气象情况!L30,IF($H$4="罗勇",全国主要城市气象情况!L34,IF($H$4="大城府",全国主要城市气象情况!L38,IF($H$4="吉隆坡",全国主要城市气象情况!L42,IF($H$4="槟城",全国主要城市气象情况!L46,IF($H$4="胡志明市",全国主要城市气象情况!L50,IF($H$4="北宁省",全国主要城市气象情况!L54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="M24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!M6,IF($H$4="华东",全国主要城市气象情况!M10,IF($H$4="华中",全国主要城市气象情况!M14,IF($H$4="西南",全国主要城市气象情况!M18,IF($H$4="西北",全国主要城市气象情况!M22,IF($H$4="华北",全国主要城市气象情况!M26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!M6,IF($H$4="华东",全国主要城市气象情况!M10,IF($H$4="华中",全国主要城市气象情况!M14,IF($H$4="西南",全国主要城市气象情况!M18,IF($H$4="西北",全国主要城市气象情况!M22,IF($H$4="华北",全国主要城市气象情况!M26,IF($H$4="曼谷",全国主要城市气象情况!M30,IF($H$4="罗勇",全国主要城市气象情况!M34,IF($H$4="大城府",全国主要城市气象情况!M38,IF($H$4="吉隆坡",全国主要城市气象情况!M42,IF($H$4="槟城",全国主要城市气象情况!M46,IF($H$4="胡志明市",全国主要城市气象情况!M50,IF($H$4="北宁省",全国主要城市气象情况!M54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="N24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!N6,IF($H$4="华东",全国主要城市气象情况!N10,IF($H$4="华中",全国主要城市气象情况!N14,IF($H$4="西南",全国主要城市气象情况!N18,IF($H$4="西北",全国主要城市气象情况!N22,IF($H$4="华北",全国主要城市气象情况!N26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!N6,IF($H$4="华东",全国主要城市气象情况!N10,IF($H$4="华中",全国主要城市气象情况!N14,IF($H$4="西南",全国主要城市气象情况!N18,IF($H$4="西北",全国主要城市气象情况!N22,IF($H$4="华北",全国主要城市气象情况!N26,IF($H$4="曼谷",全国主要城市气象情况!N30,IF($H$4="罗勇",全国主要城市气象情况!N34,IF($H$4="大城府",全国主要城市气象情况!N38,IF($H$4="吉隆坡",全国主要城市气象情况!N42,IF($H$4="槟城",全国主要城市气象情况!N46,IF($H$4="胡志明市",全国主要城市气象情况!N50,IF($H$4="北宁省",全国主要城市气象情况!N54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="O24" s="32">
-        <f>IF($H$4="华南",全国主要城市气象情况!O6,IF($H$4="华东",全国主要城市气象情况!O10,IF($H$4="华中",全国主要城市气象情况!O14,IF($H$4="西南",全国主要城市气象情况!O18,IF($H$4="西北",全国主要城市气象情况!O22,IF($H$4="华北",全国主要城市气象情况!O26,0))))))+1</f>
+        <f>IF($H$4="华南",全国主要城市气象情况!O6,IF($H$4="华东",全国主要城市气象情况!O10,IF($H$4="华中",全国主要城市气象情况!O14,IF($H$4="西南",全国主要城市气象情况!O18,IF($H$4="西北",全国主要城市气象情况!O22,IF($H$4="华北",全国主要城市气象情况!O26,IF($H$4="曼谷",全国主要城市气象情况!O30,IF($H$4="罗勇",全国主要城市气象情况!O34,IF($H$4="大城府",全国主要城市气象情况!O38,IF($H$4="吉隆坡",全国主要城市气象情况!O42,IF($H$4="槟城",全国主要城市气象情况!O46,IF($H$4="胡志明市",全国主要城市气象情况!O50,IF($H$4="北宁省",全国主要城市气象情况!O54,0)))))))))))))+1</f>
         <v>1</v>
       </c>
       <c r="P24" s="33"/>
     </row>
-    <row r="25" ht="21.95" customHeight="1" spans="2:22">
+    <row r="25" ht="21.95" customHeight="1" spans="2:16">
       <c r="B25" s="36"/>
-      <c r="C25" s="47" t="s">
-        <v>50</v>
+      <c r="C25" s="46" t="s">
+        <v>44</v>
       </c>
       <c r="D25" s="38">
-        <f>MAX(IF(D24&lt;D23,D8*0.015*(D23-D24),0),0)</f>
+        <f t="shared" ref="D25:O25" si="9">MAX(IF(D24&lt;D23,D8*0.015*(D23-D24),0),0)</f>
         <v>0</v>
       </c>
       <c r="E25" s="38">
-        <f>MAX(IF(E24&lt;E23,E8*0.015*(E23-E24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F25" s="38">
-        <f>MAX(IF(F24&lt;F23,F8*0.015*(F23-F24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G25" s="38">
-        <f>MAX(IF(G24&lt;G23,G8*0.015*(G23-G24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H25" s="38">
-        <f>MAX(IF(H24&lt;H23,H8*0.015*(H23-H24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I25" s="38">
-        <f>MAX(IF(I24&lt;I23,I8*0.015*(I23-I24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J25" s="38">
-        <f>MAX(IF(J24&lt;J23,J8*0.015*(J23-J24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K25" s="38">
-        <f>MAX(IF(K24&lt;K23,K8*0.015*(K23-K24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L25" s="38">
-        <f>MAX(IF(L24&lt;L23,L8*0.015*(L23-L24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M25" s="38">
-        <f>MAX(IF(M24&lt;M23,M8*0.015*(M23-M24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N25" s="38">
-        <f>MAX(IF(N24&lt;N23,N8*0.015*(N23-N24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O25" s="38">
-        <f>MAX(IF(O24&lt;O23,O8*0.015*(O23-O24),0),0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P25" s="39">
         <f>MAX(SUM(D25:O25),0)</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="7" t="e">
-        <f>P25/P8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V25" s="7" t="e">
-        <f>P25/P27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="26" ht="6" customHeight="1" spans="2:22">
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="51"/>
-    </row>
-    <row r="27" ht="21.95" customHeight="1" spans="2:22">
-      <c r="B27" s="52" t="s">
-        <v>51</v>
+    </row>
+    <row r="26" ht="6" customHeight="1" spans="2:16">
+      <c r="B26" s="47"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="50"/>
+    </row>
+    <row r="27" ht="21.95" customHeight="1" spans="2:16">
+      <c r="B27" s="51" t="s">
+        <v>45</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="54">
-        <f t="shared" ref="P25:P28" si="7">SUM(D27:O27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="21.95" customHeight="1" spans="2:22">
+        <v>46</v>
+      </c>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="52"/>
+      <c r="P27" s="53">
+        <f>SUM(D27:O27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="21.95" customHeight="1" spans="2:16">
       <c r="B28" s="30"/>
       <c r="C28" s="31" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D28" s="32" t="e">
-        <f t="shared" ref="D28:O28" si="8">D11+D16+D21+D25</f>
+        <f t="shared" ref="D28:O28" si="10">D11+D16+D21+D25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" s="32" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F28" s="32" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="32" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H28" s="32" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="32" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J28" s="32" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K28" s="32" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L28" s="32" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M28" s="32" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N28" s="32" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O28" s="32" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P28" s="54" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29" ht="21.95" customHeight="1" spans="2:22">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P28" s="53" t="e">
+        <f>SUM(D28:O28)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" ht="21.95" customHeight="1" spans="2:16">
       <c r="B29" s="36"/>
       <c r="C29" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="55" t="e">
+        <v>48</v>
+      </c>
+      <c r="D29" s="54" t="e">
         <f>P28/P27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E29" s="56"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="H29" s="57"/>
-      <c r="I29" s="59">
+      <c r="E29" s="55"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" s="56"/>
+      <c r="I29" s="58">
         <v>0.8</v>
       </c>
-      <c r="J29" s="56"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="M29" s="56"/>
-      <c r="N29" s="61" t="e">
+      <c r="J29" s="55"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="55"/>
+      <c r="N29" s="60" t="e">
         <f>P28*I29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="56"/>
-      <c r="P29" s="62"/>
-    </row>
-    <row r="30" spans="2:22">
-      <c r="D30" s="63" t="e">
-        <f t="shared" ref="D30:O30" si="9">D28/D27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O30" s="63" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="O29" s="55"/>
+      <c r="P29" s="61"/>
+    </row>
+    <row r="30" spans="2:16">
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -4444,8 +4263,8 @@
     <mergeCell ref="B17:B21"/>
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="B27:B29"/>
+    <mergeCell ref="H4:I6"/>
     <mergeCell ref="B3:G6"/>
-    <mergeCell ref="H4:I6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:I6">
@@ -4462,66 +4281,66 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:O27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="B2:O54"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3839285714286" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3833333333333" style="1" customWidth="1"/>
     <col min="4" max="5" width="11" style="1" customWidth="1"/>
-    <col min="6" max="14" width="12.1339285714286" style="1" customWidth="1"/>
+    <col min="6" max="14" width="12.1333333333333" style="1" customWidth="1"/>
     <col min="15" max="15" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="17" customHeight="1" spans="2:15">
       <c r="B2" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="N2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" spans="2:15">
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D3" s="3">
         <v>14.7</v>
@@ -4563,7 +4382,7 @@
     <row r="4" ht="17" customHeight="1" spans="2:15">
       <c r="B4" s="4"/>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3">
         <v>54.1</v>
@@ -4605,7 +4424,7 @@
     <row r="5" ht="17" customHeight="1" spans="2:15">
       <c r="B5" s="4"/>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D5" s="3">
         <v>9.92644743894</v>
@@ -4647,7 +4466,7 @@
     <row r="6" ht="17" customHeight="1" spans="2:15">
       <c r="B6" s="5"/>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D6" s="3">
         <v>21</v>
@@ -4688,10 +4507,10 @@
     </row>
     <row r="7" ht="17" customHeight="1" spans="2:15">
       <c r="B7" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D7" s="3">
         <v>6.6</v>
@@ -4733,7 +4552,7 @@
     <row r="8" ht="17" customHeight="1" spans="2:15">
       <c r="B8" s="4"/>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D8" s="3">
         <v>71</v>
@@ -4775,7 +4594,7 @@
     <row r="9" ht="17" customHeight="1" spans="2:15">
       <c r="B9" s="4"/>
       <c r="C9" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3">
         <v>4.3157967952</v>
@@ -4817,7 +4636,7 @@
     <row r="10" ht="17" customHeight="1" spans="2:15">
       <c r="B10" s="5"/>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3">
         <v>21</v>
@@ -4858,10 +4677,10 @@
     </row>
     <row r="11" ht="17" customHeight="1" spans="2:15">
       <c r="B11" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D11" s="3">
         <v>4.7</v>
@@ -4903,7 +4722,7 @@
     <row r="12" ht="17" customHeight="1" spans="2:15">
       <c r="B12" s="4"/>
       <c r="C12" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D12" s="3">
         <v>85</v>
@@ -4945,7 +4764,7 @@
     <row r="13" ht="17" customHeight="1" spans="2:15">
       <c r="B13" s="4"/>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D13" s="3">
         <v>3.7132789735</v>
@@ -4987,7 +4806,7 @@
     <row r="14" ht="17" customHeight="1" spans="2:15">
       <c r="B14" s="5"/>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D14" s="3">
         <v>21</v>
@@ -5028,10 +4847,10 @@
     </row>
     <row r="15" ht="17" customHeight="1" spans="2:15">
       <c r="B15" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D15" s="3">
         <v>7.5</v>
@@ -5073,7 +4892,7 @@
     <row r="16" ht="17" customHeight="1" spans="2:15">
       <c r="B16" s="4"/>
       <c r="C16" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D16" s="3">
         <v>84</v>
@@ -5115,7 +4934,7 @@
     <row r="17" ht="17" customHeight="1" spans="2:15">
       <c r="B17" s="4"/>
       <c r="C17" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D17" s="3">
         <v>6.298148725</v>
@@ -5157,7 +4976,7 @@
     <row r="18" ht="17" customHeight="1" spans="2:15">
       <c r="B18" s="5"/>
       <c r="C18" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" s="3">
         <v>21</v>
@@ -5198,10 +5017,10 @@
     </row>
     <row r="19" ht="17" customHeight="1" spans="2:15">
       <c r="B19" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" s="3">
         <v>2.4</v>
@@ -5243,7 +5062,7 @@
     <row r="20" ht="17" customHeight="1" spans="2:15">
       <c r="B20" s="4"/>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D20" s="3">
         <v>67</v>
@@ -5285,7 +5104,7 @@
     <row r="21" ht="17" customHeight="1" spans="2:15">
       <c r="B21" s="4"/>
       <c r="C21" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D21" s="3">
         <v>0.1031318424</v>
@@ -5327,7 +5146,7 @@
     <row r="22" ht="17" customHeight="1" spans="2:15">
       <c r="B22" s="5"/>
       <c r="C22" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D22" s="3">
         <v>21</v>
@@ -5368,10 +5187,10 @@
     </row>
     <row r="23" ht="17" customHeight="1" spans="2:15">
       <c r="B23" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D23" s="3">
         <v>1.3</v>
@@ -5413,7 +5232,7 @@
     <row r="24" ht="17" customHeight="1" spans="2:15">
       <c r="B24" s="4"/>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D24" s="3">
         <v>56</v>
@@ -5455,7 +5274,7 @@
     <row r="25" ht="17" customHeight="1" spans="2:15">
       <c r="B25" s="4"/>
       <c r="C25" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3">
         <v>-1.6592527222</v>
@@ -5497,7 +5316,7 @@
     <row r="26" ht="17" customHeight="1" spans="2:15">
       <c r="B26" s="5"/>
       <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D26" s="3">
         <v>21</v>
@@ -5536,15 +5355,1211 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" ht="17.55"/>
+    <row r="27" spans="2:15">
+      <c r="B27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="3">
+        <v>26.8</v>
+      </c>
+      <c r="E27" s="3">
+        <v>28.2</v>
+      </c>
+      <c r="F27" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="G27" s="3">
+        <v>30.1</v>
+      </c>
+      <c r="H27" s="3">
+        <v>29.8</v>
+      </c>
+      <c r="I27" s="3">
+        <v>29.2</v>
+      </c>
+      <c r="J27" s="3">
+        <v>28.9</v>
+      </c>
+      <c r="K27" s="3">
+        <v>28.7</v>
+      </c>
+      <c r="L27" s="3">
+        <v>28.5</v>
+      </c>
+      <c r="M27" s="3">
+        <v>28.1</v>
+      </c>
+      <c r="N27" s="3">
+        <v>27.4</v>
+      </c>
+      <c r="O27">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="B28" s="4"/>
+      <c r="C28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="3">
+        <v>68</v>
+      </c>
+      <c r="E28" s="3">
+        <v>72</v>
+      </c>
+      <c r="F28" s="3">
+        <v>75</v>
+      </c>
+      <c r="G28" s="3">
+        <v>77</v>
+      </c>
+      <c r="H28" s="3">
+        <v>78</v>
+      </c>
+      <c r="I28" s="3">
+        <v>77</v>
+      </c>
+      <c r="J28" s="3">
+        <v>76</v>
+      </c>
+      <c r="K28" s="3">
+        <v>77</v>
+      </c>
+      <c r="L28" s="3">
+        <v>79</v>
+      </c>
+      <c r="M28" s="3">
+        <v>78</v>
+      </c>
+      <c r="N28" s="3">
+        <v>74</v>
+      </c>
+      <c r="O28">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="B29" s="4"/>
+      <c r="C29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="3">
+        <v>22.3207</v>
+      </c>
+      <c r="E29" s="3">
+        <v>24.2193</v>
+      </c>
+      <c r="F29" s="3">
+        <v>25.8016</v>
+      </c>
+      <c r="G29" s="3">
+        <v>26.7702</v>
+      </c>
+      <c r="H29" s="3">
+        <v>26.6361</v>
+      </c>
+      <c r="I29" s="3">
+        <v>25.9134</v>
+      </c>
+      <c r="J29" s="3">
+        <v>25.4784</v>
+      </c>
+      <c r="K29" s="3">
+        <v>25.4375</v>
+      </c>
+      <c r="L29" s="3">
+        <v>25.5425</v>
+      </c>
+      <c r="M29" s="3">
+        <v>25.0132</v>
+      </c>
+      <c r="N29" s="3">
+        <v>23.7629</v>
+      </c>
+      <c r="O29">
+        <v>22.1894</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="B30" s="5"/>
+      <c r="C30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="3">
+        <v>26.82</v>
+      </c>
+      <c r="E30" s="3">
+        <v>28.72</v>
+      </c>
+      <c r="F30" s="3">
+        <v>30.3</v>
+      </c>
+      <c r="G30" s="3">
+        <v>31.27</v>
+      </c>
+      <c r="H30" s="3">
+        <v>31.14</v>
+      </c>
+      <c r="I30" s="3">
+        <v>30.41</v>
+      </c>
+      <c r="J30" s="3">
+        <v>29.98</v>
+      </c>
+      <c r="K30" s="3">
+        <v>29.94</v>
+      </c>
+      <c r="L30" s="3">
+        <v>30.04</v>
+      </c>
+      <c r="M30" s="3">
+        <v>29.51</v>
+      </c>
+      <c r="N30" s="3">
+        <v>28.26</v>
+      </c>
+      <c r="O30">
+        <v>26.69</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="B31" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="3">
+        <v>26.2</v>
+      </c>
+      <c r="E31" s="3">
+        <v>27.8</v>
+      </c>
+      <c r="F31" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="G31" s="3">
+        <v>29.8</v>
+      </c>
+      <c r="H31" s="3">
+        <v>29.5</v>
+      </c>
+      <c r="I31" s="3">
+        <v>28.9</v>
+      </c>
+      <c r="J31" s="3">
+        <v>28.6</v>
+      </c>
+      <c r="K31" s="3">
+        <v>28.4</v>
+      </c>
+      <c r="L31" s="3">
+        <v>28.2</v>
+      </c>
+      <c r="M31" s="3">
+        <v>27.8</v>
+      </c>
+      <c r="N31" s="3">
+        <v>27.1</v>
+      </c>
+      <c r="O31">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15">
+      <c r="B32" s="4"/>
+      <c r="C32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="3">
+        <v>65</v>
+      </c>
+      <c r="E32" s="3">
+        <v>69</v>
+      </c>
+      <c r="F32" s="3">
+        <v>72</v>
+      </c>
+      <c r="G32" s="3">
+        <v>74</v>
+      </c>
+      <c r="H32" s="3">
+        <v>75</v>
+      </c>
+      <c r="I32" s="3">
+        <v>74</v>
+      </c>
+      <c r="J32" s="3">
+        <v>73</v>
+      </c>
+      <c r="K32" s="3">
+        <v>74</v>
+      </c>
+      <c r="L32" s="3">
+        <v>76</v>
+      </c>
+      <c r="M32" s="3">
+        <v>75</v>
+      </c>
+      <c r="N32" s="3">
+        <v>71</v>
+      </c>
+      <c r="O32">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15">
+      <c r="B33" s="4"/>
+      <c r="C33" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="3">
+        <v>21.3259</v>
+      </c>
+      <c r="E33" s="3">
+        <v>23.3964</v>
+      </c>
+      <c r="F33" s="3">
+        <v>25.0631</v>
+      </c>
+      <c r="G33" s="3">
+        <v>26.0271</v>
+      </c>
+      <c r="H33" s="3">
+        <v>25.8962</v>
+      </c>
+      <c r="I33" s="3">
+        <v>25.178</v>
+      </c>
+      <c r="J33" s="3">
+        <v>24.7449</v>
+      </c>
+      <c r="K33" s="3">
+        <v>24.7063</v>
+      </c>
+      <c r="L33" s="3">
+        <v>24.814</v>
+      </c>
+      <c r="M33" s="3">
+        <v>24.2876</v>
+      </c>
+      <c r="N33" s="3">
+        <v>23.0413</v>
+      </c>
+      <c r="O33">
+        <v>21.2892</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15">
+      <c r="B34" s="5"/>
+      <c r="C34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="3">
+        <v>25.83</v>
+      </c>
+      <c r="E34" s="3">
+        <v>27.9</v>
+      </c>
+      <c r="F34" s="3">
+        <v>29.56</v>
+      </c>
+      <c r="G34" s="3">
+        <v>30.53</v>
+      </c>
+      <c r="H34" s="3">
+        <v>30.4</v>
+      </c>
+      <c r="I34" s="3">
+        <v>29.68</v>
+      </c>
+      <c r="J34" s="3">
+        <v>29.24</v>
+      </c>
+      <c r="K34" s="3">
+        <v>29.21</v>
+      </c>
+      <c r="L34" s="3">
+        <v>29.31</v>
+      </c>
+      <c r="M34" s="3">
+        <v>28.79</v>
+      </c>
+      <c r="N34" s="3">
+        <v>27.54</v>
+      </c>
+      <c r="O34">
+        <v>25.79</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15">
+      <c r="B35" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="E35" s="3">
+        <v>28</v>
+      </c>
+      <c r="F35" s="3">
+        <v>29.2</v>
+      </c>
+      <c r="G35" s="3">
+        <v>29.9</v>
+      </c>
+      <c r="H35" s="3">
+        <v>29.6</v>
+      </c>
+      <c r="I35" s="3">
+        <v>29</v>
+      </c>
+      <c r="J35" s="3">
+        <v>28.7</v>
+      </c>
+      <c r="K35" s="3">
+        <v>28.5</v>
+      </c>
+      <c r="L35" s="3">
+        <v>28.3</v>
+      </c>
+      <c r="M35" s="3">
+        <v>27.9</v>
+      </c>
+      <c r="N35" s="3">
+        <v>27.2</v>
+      </c>
+      <c r="O35">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15">
+      <c r="B36" s="4"/>
+      <c r="C36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="3">
+        <v>67</v>
+      </c>
+      <c r="E36" s="3">
+        <v>71</v>
+      </c>
+      <c r="F36" s="3">
+        <v>74</v>
+      </c>
+      <c r="G36" s="3">
+        <v>76</v>
+      </c>
+      <c r="H36" s="3">
+        <v>77</v>
+      </c>
+      <c r="I36" s="3">
+        <v>76</v>
+      </c>
+      <c r="J36" s="3">
+        <v>75</v>
+      </c>
+      <c r="K36" s="3">
+        <v>76</v>
+      </c>
+      <c r="L36" s="3">
+        <v>78</v>
+      </c>
+      <c r="M36" s="3">
+        <v>77</v>
+      </c>
+      <c r="N36" s="3">
+        <v>73</v>
+      </c>
+      <c r="O36">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15">
+      <c r="B37" s="4"/>
+      <c r="C37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="3">
+        <v>21.8962</v>
+      </c>
+      <c r="E37" s="3">
+        <v>23.8825</v>
+      </c>
+      <c r="F37" s="3">
+        <v>25.4611</v>
+      </c>
+      <c r="G37" s="3">
+        <v>26.4275</v>
+      </c>
+      <c r="H37" s="3">
+        <v>26.2942</v>
+      </c>
+      <c r="I37" s="3">
+        <v>25.5733</v>
+      </c>
+      <c r="J37" s="3">
+        <v>25.1392</v>
+      </c>
+      <c r="K37" s="3">
+        <v>25.0988</v>
+      </c>
+      <c r="L37" s="3">
+        <v>25.2041</v>
+      </c>
+      <c r="M37" s="3">
+        <v>24.676</v>
+      </c>
+      <c r="N37" s="3">
+        <v>23.4282</v>
+      </c>
+      <c r="O37">
+        <v>21.858</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15">
+      <c r="B38" s="5"/>
+      <c r="C38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="3">
+        <v>26.4</v>
+      </c>
+      <c r="E38" s="3">
+        <v>28.38</v>
+      </c>
+      <c r="F38" s="3">
+        <v>29.96</v>
+      </c>
+      <c r="G38" s="3">
+        <v>30.93</v>
+      </c>
+      <c r="H38" s="3">
+        <v>30.79</v>
+      </c>
+      <c r="I38" s="3">
+        <v>30.07</v>
+      </c>
+      <c r="J38" s="3">
+        <v>29.64</v>
+      </c>
+      <c r="K38" s="3">
+        <v>29.6</v>
+      </c>
+      <c r="L38" s="3">
+        <v>29.7</v>
+      </c>
+      <c r="M38" s="3">
+        <v>29.18</v>
+      </c>
+      <c r="N38" s="3">
+        <v>27.93</v>
+      </c>
+      <c r="O38">
+        <v>26.36</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15">
+      <c r="B39" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D39" s="3">
+        <v>27.2</v>
+      </c>
+      <c r="E39" s="3">
+        <v>28.1</v>
+      </c>
+      <c r="F39" s="3">
+        <v>28.8</v>
+      </c>
+      <c r="G39" s="3">
+        <v>29.2</v>
+      </c>
+      <c r="H39" s="3">
+        <v>29</v>
+      </c>
+      <c r="I39" s="3">
+        <v>28.5</v>
+      </c>
+      <c r="J39" s="3">
+        <v>28.2</v>
+      </c>
+      <c r="K39" s="3">
+        <v>28.1</v>
+      </c>
+      <c r="L39" s="3">
+        <v>28</v>
+      </c>
+      <c r="M39" s="3">
+        <v>27.8</v>
+      </c>
+      <c r="N39" s="3">
+        <v>27.4</v>
+      </c>
+      <c r="O39">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15">
+      <c r="B40" s="4"/>
+      <c r="C40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="3">
+        <v>82</v>
+      </c>
+      <c r="E40" s="3">
+        <v>84</v>
+      </c>
+      <c r="F40" s="3">
+        <v>86</v>
+      </c>
+      <c r="G40" s="3">
+        <v>87</v>
+      </c>
+      <c r="H40" s="3">
+        <v>88</v>
+      </c>
+      <c r="I40" s="3">
+        <v>86</v>
+      </c>
+      <c r="J40" s="3">
+        <v>85</v>
+      </c>
+      <c r="K40" s="3">
+        <v>86</v>
+      </c>
+      <c r="L40" s="3">
+        <v>87</v>
+      </c>
+      <c r="M40" s="3">
+        <v>86</v>
+      </c>
+      <c r="N40" s="3">
+        <v>84</v>
+      </c>
+      <c r="O40">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15">
+      <c r="B41" s="4"/>
+      <c r="C41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="3">
+        <v>24.7278</v>
+      </c>
+      <c r="E41" s="3">
+        <v>25.8862</v>
+      </c>
+      <c r="F41" s="3">
+        <v>26.8574</v>
+      </c>
+      <c r="G41" s="3">
+        <v>27.394</v>
+      </c>
+      <c r="H41" s="3">
+        <v>27.3441</v>
+      </c>
+      <c r="I41" s="3">
+        <v>26.5648</v>
+      </c>
+      <c r="J41" s="3">
+        <v>26.1278</v>
+      </c>
+      <c r="K41" s="3">
+        <v>26.1746</v>
+      </c>
+      <c r="L41" s="3">
+        <v>26.2206</v>
+      </c>
+      <c r="M41" s="3">
+        <v>25.882</v>
+      </c>
+      <c r="N41" s="3">
+        <v>25.2069</v>
+      </c>
+      <c r="O41">
+        <v>24.6769</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15">
+      <c r="B42" s="5"/>
+      <c r="C42" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="3">
+        <v>29.23</v>
+      </c>
+      <c r="E42" s="3">
+        <v>30.39</v>
+      </c>
+      <c r="F42" s="3">
+        <v>31.36</v>
+      </c>
+      <c r="G42" s="3">
+        <v>31.89</v>
+      </c>
+      <c r="H42" s="3">
+        <v>31.84</v>
+      </c>
+      <c r="I42" s="3">
+        <v>31.06</v>
+      </c>
+      <c r="J42" s="3">
+        <v>30.63</v>
+      </c>
+      <c r="K42" s="3">
+        <v>30.67</v>
+      </c>
+      <c r="L42" s="3">
+        <v>30.72</v>
+      </c>
+      <c r="M42" s="3">
+        <v>30.38</v>
+      </c>
+      <c r="N42" s="3">
+        <v>29.71</v>
+      </c>
+      <c r="O42">
+        <v>29.18</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15">
+      <c r="B43" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="3">
+        <v>26.8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>27.6</v>
+      </c>
+      <c r="F43" s="3">
+        <v>28.3</v>
+      </c>
+      <c r="G43" s="3">
+        <v>28.7</v>
+      </c>
+      <c r="H43" s="3">
+        <v>28.5</v>
+      </c>
+      <c r="I43" s="3">
+        <v>28</v>
+      </c>
+      <c r="J43" s="3">
+        <v>27.7</v>
+      </c>
+      <c r="K43" s="3">
+        <v>27.6</v>
+      </c>
+      <c r="L43" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="M43" s="3">
+        <v>27.3</v>
+      </c>
+      <c r="N43" s="3">
+        <v>26.9</v>
+      </c>
+      <c r="O43">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15">
+      <c r="B44" s="4"/>
+      <c r="C44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="3">
+        <v>80</v>
+      </c>
+      <c r="E44" s="3">
+        <v>82</v>
+      </c>
+      <c r="F44" s="3">
+        <v>84</v>
+      </c>
+      <c r="G44" s="3">
+        <v>85</v>
+      </c>
+      <c r="H44" s="3">
+        <v>86</v>
+      </c>
+      <c r="I44" s="3">
+        <v>84</v>
+      </c>
+      <c r="J44" s="3">
+        <v>83</v>
+      </c>
+      <c r="K44" s="3">
+        <v>84</v>
+      </c>
+      <c r="L44" s="3">
+        <v>85</v>
+      </c>
+      <c r="M44" s="3">
+        <v>84</v>
+      </c>
+      <c r="N44" s="3">
+        <v>82</v>
+      </c>
+      <c r="O44">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15">
+      <c r="B45" s="4"/>
+      <c r="C45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="3">
+        <v>24.0576</v>
+      </c>
+      <c r="E45" s="3">
+        <v>25.114</v>
+      </c>
+      <c r="F45" s="3">
+        <v>26.0803</v>
+      </c>
+      <c r="G45" s="3">
+        <v>26.6143</v>
+      </c>
+      <c r="H45" s="3">
+        <v>26.5648</v>
+      </c>
+      <c r="I45" s="3">
+        <v>25.7892</v>
+      </c>
+      <c r="J45" s="3">
+        <v>25.3544</v>
+      </c>
+      <c r="K45" s="3">
+        <v>25.401</v>
+      </c>
+      <c r="L45" s="3">
+        <v>25.4468</v>
+      </c>
+      <c r="M45" s="3">
+        <v>25.1099</v>
+      </c>
+      <c r="N45" s="3">
+        <v>24.4383</v>
+      </c>
+      <c r="O45">
+        <v>23.911</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15">
+      <c r="B46" s="5"/>
+      <c r="C46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="3">
+        <v>28.56</v>
+      </c>
+      <c r="E46" s="3">
+        <v>29.61</v>
+      </c>
+      <c r="F46" s="3">
+        <v>30.58</v>
+      </c>
+      <c r="G46" s="3">
+        <v>31.11</v>
+      </c>
+      <c r="H46" s="3">
+        <v>31.06</v>
+      </c>
+      <c r="I46" s="3">
+        <v>30.29</v>
+      </c>
+      <c r="J46" s="3">
+        <v>29.85</v>
+      </c>
+      <c r="K46" s="3">
+        <v>29.9</v>
+      </c>
+      <c r="L46" s="3">
+        <v>29.95</v>
+      </c>
+      <c r="M46" s="3">
+        <v>29.61</v>
+      </c>
+      <c r="N46" s="3">
+        <v>28.94</v>
+      </c>
+      <c r="O46">
+        <v>28.41</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15">
+      <c r="B47" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" s="3">
+        <v>26</v>
+      </c>
+      <c r="E47" s="3">
+        <v>27.8</v>
+      </c>
+      <c r="F47" s="3">
+        <v>29.2</v>
+      </c>
+      <c r="G47" s="3">
+        <v>30.1</v>
+      </c>
+      <c r="H47" s="3">
+        <v>29.8</v>
+      </c>
+      <c r="I47" s="3">
+        <v>28.9</v>
+      </c>
+      <c r="J47" s="3">
+        <v>28.5</v>
+      </c>
+      <c r="K47" s="3">
+        <v>28.3</v>
+      </c>
+      <c r="L47" s="3">
+        <v>28.1</v>
+      </c>
+      <c r="M47" s="3">
+        <v>27.7</v>
+      </c>
+      <c r="N47" s="3">
+        <v>26.8</v>
+      </c>
+      <c r="O47">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15">
+      <c r="B48" s="4"/>
+      <c r="C48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="3">
+        <v>75</v>
+      </c>
+      <c r="E48" s="3">
+        <v>78</v>
+      </c>
+      <c r="F48" s="3">
+        <v>80</v>
+      </c>
+      <c r="G48" s="3">
+        <v>82</v>
+      </c>
+      <c r="H48" s="3">
+        <v>83</v>
+      </c>
+      <c r="I48" s="3">
+        <v>81</v>
+      </c>
+      <c r="J48" s="3">
+        <v>80</v>
+      </c>
+      <c r="K48" s="3">
+        <v>81</v>
+      </c>
+      <c r="L48" s="3">
+        <v>82</v>
+      </c>
+      <c r="M48" s="3">
+        <v>81</v>
+      </c>
+      <c r="N48" s="3">
+        <v>78</v>
+      </c>
+      <c r="O48">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15">
+      <c r="B49" s="4"/>
+      <c r="C49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="3">
+        <v>22.5842</v>
+      </c>
+      <c r="E49" s="3">
+        <v>24.7268</v>
+      </c>
+      <c r="F49" s="3">
+        <v>26.3617</v>
+      </c>
+      <c r="G49" s="3">
+        <v>27.5272</v>
+      </c>
+      <c r="H49" s="3">
+        <v>27.3869</v>
+      </c>
+      <c r="I49" s="3">
+        <v>26.2214</v>
+      </c>
+      <c r="J49" s="3">
+        <v>25.6896</v>
+      </c>
+      <c r="K49" s="3">
+        <v>25.6438</v>
+      </c>
+      <c r="L49" s="3">
+        <v>25.5966</v>
+      </c>
+      <c r="M49" s="3">
+        <v>25.0662</v>
+      </c>
+      <c r="N49" s="3">
+        <v>23.7721</v>
+      </c>
+      <c r="O49">
+        <v>22.5362</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15">
+      <c r="B50" s="5"/>
+      <c r="C50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50" s="3">
+        <v>27.08</v>
+      </c>
+      <c r="E50" s="3">
+        <v>29.23</v>
+      </c>
+      <c r="F50" s="3">
+        <v>30.86</v>
+      </c>
+      <c r="G50" s="3">
+        <v>32.03</v>
+      </c>
+      <c r="H50" s="3">
+        <v>31.89</v>
+      </c>
+      <c r="I50" s="3">
+        <v>30.72</v>
+      </c>
+      <c r="J50" s="3">
+        <v>30.19</v>
+      </c>
+      <c r="K50" s="3">
+        <v>30.14</v>
+      </c>
+      <c r="L50" s="3">
+        <v>30.1</v>
+      </c>
+      <c r="M50" s="3">
+        <v>29.57</v>
+      </c>
+      <c r="N50" s="3">
+        <v>28.27</v>
+      </c>
+      <c r="O50">
+        <v>27.04</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15">
+      <c r="B51" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="E51" s="3">
+        <v>20.2</v>
+      </c>
+      <c r="F51" s="3">
+        <v>23.8</v>
+      </c>
+      <c r="G51" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="H51" s="3">
+        <v>28.9</v>
+      </c>
+      <c r="I51" s="3">
+        <v>30.1</v>
+      </c>
+      <c r="J51" s="3">
+        <v>30.3</v>
+      </c>
+      <c r="K51" s="3">
+        <v>29.8</v>
+      </c>
+      <c r="L51" s="3">
+        <v>28.2</v>
+      </c>
+      <c r="M51" s="3">
+        <v>25.4</v>
+      </c>
+      <c r="N51" s="3">
+        <v>22.1</v>
+      </c>
+      <c r="O51">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15">
+      <c r="B52" s="4"/>
+      <c r="C52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52" s="3">
+        <v>78</v>
+      </c>
+      <c r="E52" s="3">
+        <v>82</v>
+      </c>
+      <c r="F52" s="3">
+        <v>85</v>
+      </c>
+      <c r="G52" s="3">
+        <v>86</v>
+      </c>
+      <c r="H52" s="3">
+        <v>84</v>
+      </c>
+      <c r="I52" s="3">
+        <v>82</v>
+      </c>
+      <c r="J52" s="3">
+        <v>80</v>
+      </c>
+      <c r="K52" s="3">
+        <v>82</v>
+      </c>
+      <c r="L52" s="3">
+        <v>84</v>
+      </c>
+      <c r="M52" s="3">
+        <v>83</v>
+      </c>
+      <c r="N52" s="3">
+        <v>80</v>
+      </c>
+      <c r="O52">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15">
+      <c r="B53" s="4"/>
+      <c r="C53" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="3">
+        <v>15.8485</v>
+      </c>
+      <c r="E53" s="3">
+        <v>17.9708</v>
+      </c>
+      <c r="F53" s="3">
+        <v>21.8471</v>
+      </c>
+      <c r="G53" s="3">
+        <v>24.614</v>
+      </c>
+      <c r="H53" s="3">
+        <v>26.6625</v>
+      </c>
+      <c r="I53" s="3">
+        <v>27.5272</v>
+      </c>
+      <c r="J53" s="3">
+        <v>27.4177</v>
+      </c>
+      <c r="K53" s="3">
+        <v>27.2376</v>
+      </c>
+      <c r="L53" s="3">
+        <v>25.9833</v>
+      </c>
+      <c r="M53" s="3">
+        <v>23.1283</v>
+      </c>
+      <c r="N53" s="3">
+        <v>19.5454</v>
+      </c>
+      <c r="O53">
+        <v>16.639</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15">
+      <c r="B54" s="5"/>
+      <c r="C54" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54" s="3">
+        <v>21</v>
+      </c>
+      <c r="E54" s="3">
+        <v>22.47</v>
+      </c>
+      <c r="F54" s="3">
+        <v>26.35</v>
+      </c>
+      <c r="G54" s="3">
+        <v>29.11</v>
+      </c>
+      <c r="H54" s="3">
+        <v>31.16</v>
+      </c>
+      <c r="I54" s="3">
+        <v>32.03</v>
+      </c>
+      <c r="J54" s="3">
+        <v>31.92</v>
+      </c>
+      <c r="K54" s="3">
+        <v>31.74</v>
+      </c>
+      <c r="L54" s="3">
+        <v>30.48</v>
+      </c>
+      <c r="M54" s="3">
+        <v>27.63</v>
+      </c>
+      <c r="N54" s="3">
+        <v>24.05</v>
+      </c>
+      <c r="O54">
+        <v>21.14</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="13">
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="B15:B18"/>
     <mergeCell ref="B19:B22"/>
     <mergeCell ref="B23:B26"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="B51:B54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
